--- a/output/balance_sheet_templates/us_saf_bal_sheets.xlsx
+++ b/output/balance_sheet_templates/us_saf_bal_sheets.xlsx
@@ -1347,12 +1347,24 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="B26" s="8" t="n">
+        <v>0.04159</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>0.289825</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.100937</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.833897</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>8.478849</v>
+      </c>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
@@ -1370,6 +1382,21 @@
           <t>Feb</t>
         </is>
       </c>
+      <c r="C27" t="n">
+        <v>0.294725</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.10887</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.578596</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.254939</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15.728119</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1377,12 +1404,24 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
+      <c r="B28" s="8" t="n">
+        <v>0.280826</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>0.288906</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>1.026537</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.79717</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>2.119258</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>3.845015</v>
+      </c>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
@@ -1400,6 +1439,24 @@
           <t>Apr</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>1.234442</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.293289</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.408991</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.913521</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.781201</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13.42833</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1408,11 +1465,21 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
+      <c r="C30" s="8" t="n">
+        <v>0.287496</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0.202831</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>1.626715</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>3.266216</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>18.928087</v>
+      </c>
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="8" t="n"/>
@@ -1430,6 +1497,24 @@
           <t>Jun</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>0.508513</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.357317</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.802264</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.121861</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.998612</v>
+      </c>
+      <c r="G31" t="n">
+        <v>18.031739</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1437,12 +1522,24 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
+      <c r="B32" s="8" t="n">
+        <v>1.536725</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1.093159</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>1.137973</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>1.770762</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>3.256887</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>25.152725</v>
+      </c>
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="8" t="n"/>
       <c r="J32" s="8" t="n"/>
@@ -1460,6 +1557,24 @@
           <t>Aug</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>0.063855</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.722058</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.392568</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.911842</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.02679</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9.80057</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1467,12 +1582,24 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
+      <c r="B34" s="8" t="n">
+        <v>0.371169</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>0.300122</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>0.393571</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.6593020000000001</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>9.238825</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>22.281075</v>
+      </c>
       <c r="H34" s="8" t="n"/>
       <c r="I34" s="8" t="n"/>
       <c r="J34" s="8" t="n"/>
@@ -1490,6 +1617,24 @@
           <t>Oct</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>0.188416</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.437741</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.764631</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.953292</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.385772</v>
+      </c>
+      <c r="G35" t="n">
+        <v>26.607638</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1497,12 +1642,24 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
+      <c r="B36" s="8" t="n">
+        <v>0.188201</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>0.406932</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>0.152226</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.449778</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>2.385423</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>33.573929</v>
+      </c>
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="8" t="n"/>
       <c r="J36" s="8" t="n"/>
@@ -1520,6 +1677,24 @@
           <t>Dec</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>0.194662</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.308503</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.100555</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.132329</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.166746</v>
+      </c>
+      <c r="G37" t="n">
+        <v>44.299391</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
@@ -1660,13 +1835,27 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
+      <c r="B42" s="8" t="n">
+        <v>0.0046053</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>0.0002408</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0.008428</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.00585746</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0.0046053</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>0.03396183</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0.016555</v>
+      </c>
       <c r="I42" s="8" t="n"/>
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="8" t="n"/>
@@ -1683,6 +1872,24 @@
           <t>Feb</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>0.0002408</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.004718175</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.02876958</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.02728264</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.04106242</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.04555334</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -1690,13 +1897,25 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
+      <c r="B44" s="8" t="n">
+        <v>0.0004816</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>0.02100077</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>0.06967638299999999</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.04181191</v>
+      </c>
       <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="G44" s="8" t="n">
+        <v>0.02056733</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0.023783214</v>
+      </c>
       <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="8" t="n"/>
@@ -1713,6 +1932,24 @@
           <t>Apr</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>0.0142975</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.01576036</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01903825</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.01202495</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.00284445</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.026640005</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1720,12 +1957,24 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
+      <c r="B46" s="8" t="n">
+        <v>0.01209719</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>0.0266686</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>0.010180723</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.005852945</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>0.0246519</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>0.03919321</v>
+      </c>
       <c r="H46" s="8" t="n"/>
       <c r="I46" s="8" t="n"/>
       <c r="J46" s="8" t="n"/>
@@ -1743,6 +1992,24 @@
           <t>Jun</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>0.010004939</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.03658956</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.05091114</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.016555</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.01641654</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.01078483</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1750,12 +2017,24 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
+      <c r="B48" s="8" t="n">
+        <v>0.0046053</v>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>0.021255115</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>0.03958752</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.012642</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0.04215806</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>0.0224546</v>
+      </c>
       <c r="H48" s="8" t="n"/>
       <c r="I48" s="8" t="n"/>
       <c r="J48" s="8" t="n"/>
@@ -1773,6 +2052,24 @@
           <t>Aug</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>0.003757383</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.01818642</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.06362538</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0090601</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.048513675</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.01508612</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1780,12 +2077,24 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
+      <c r="B50" s="8" t="n">
+        <v>0.009210599999999999</v>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>0.004214</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>0.037076578</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.0008428</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>0.052301158</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>0.01635032</v>
+      </c>
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n"/>
@@ -1803,6 +2112,24 @@
           <t>Oct</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>0.0007224</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.02221982</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0389494</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.02583182</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.03093678</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.01376172</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -1810,12 +2137,24 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
+      <c r="B52" s="8" t="n">
+        <v>0.0094514</v>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>0.02121147</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>0.018569593</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.01201592</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>0.04286842</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>0.027699826</v>
+      </c>
       <c r="H52" s="8" t="n"/>
       <c r="I52" s="8" t="n"/>
       <c r="J52" s="8" t="n"/>
@@ -1833,6 +2172,24 @@
           <t>Dec</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>0.0004816</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.007765499</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.00179095</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.000301</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.02492882</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0054481</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -1974,12 +2331,24 @@
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
+      <c r="C58" s="8" t="n">
+        <v>0.012428892</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>0.01392426</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.0043344</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>0.011027737</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>0.018111471</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>0.0001505</v>
+      </c>
       <c r="I58" s="8" t="n"/>
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
@@ -1996,6 +2365,18 @@
           <t>Feb</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>0.0010836</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.00958986</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.000719089</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.00479493</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2004,11 +2385,17 @@
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
+      <c r="C60" s="8" t="n">
+        <v>0.02907058</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>0.00912933</v>
+      </c>
       <c r="E60" s="8" t="n"/>
       <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
+      <c r="G60" s="8" t="n">
+        <v>0.002930235</v>
+      </c>
       <c r="H60" s="8" t="n"/>
       <c r="I60" s="8" t="n"/>
       <c r="J60" s="8" t="n"/>
@@ -2026,6 +2413,15 @@
           <t>Apr</t>
         </is>
       </c>
+      <c r="C61" t="n">
+        <v>0.02876958</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.03310398</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.005525758</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2034,9 +2430,15 @@
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
+      <c r="C62" s="8" t="n">
+        <v>0.03180366</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>0.015251971</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0.011726358</v>
+      </c>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
@@ -2056,6 +2458,18 @@
           <t>Jun</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>0.004915029</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0043344</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.062717865</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.01057112</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2063,11 +2477,19 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
+      <c r="B64" s="8" t="n">
+        <v>0.024094749</v>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>0.03120768</v>
+      </c>
       <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
+      <c r="E64" s="8" t="n">
+        <v>0.00277522</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>0.027359696</v>
+      </c>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
       <c r="I64" s="8" t="n"/>
@@ -2086,6 +2508,18 @@
           <t>Aug</t>
         </is>
       </c>
+      <c r="B65" t="n">
+        <v>0.00498456</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.00958986</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.001108583</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.019438279</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -2093,12 +2527,20 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="B66" s="8" t="n"/>
+      <c r="B66" s="8" t="n">
+        <v>0.006432069</v>
+      </c>
       <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
+      <c r="D66" s="8" t="n">
+        <v>0.017664185</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.00038227</v>
+      </c>
       <c r="F66" s="8" t="n"/>
-      <c r="G66" s="8" t="n"/>
+      <c r="G66" s="8" t="n">
+        <v>0.01770482</v>
+      </c>
       <c r="H66" s="8" t="n"/>
       <c r="I66" s="8" t="n"/>
       <c r="J66" s="8" t="n"/>
@@ -2116,6 +2558,15 @@
           <t>Oct</t>
         </is>
       </c>
+      <c r="B67" t="n">
+        <v>0.025201225</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.006957314</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.01057112</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -2124,11 +2575,21 @@
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
-      <c r="G68" s="8" t="n"/>
+      <c r="C68" s="8" t="n">
+        <v>0.02397465</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>0.0043344</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.000367822</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>0.00528556</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>0.004528545</v>
+      </c>
       <c r="H68" s="8" t="n"/>
       <c r="I68" s="8" t="n"/>
       <c r="J68" s="8" t="n"/>
@@ -2145,6 +2606,18 @@
         <is>
           <t>Dec</t>
         </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.016782255</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.018804072</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.000497854</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.000266385</v>
       </c>
     </row>
     <row r="70">
